--- a/data/WP18/WP18_auswertung_parteien.xlsx
+++ b/data/WP18/WP18_auswertung_parteien.xlsx
@@ -420,7 +420,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C4" t="n">
         <v>36.779694757797</v>
@@ -429,7 +429,7 @@
         <v>1119</v>
       </c>
       <c r="E4" t="n">
-        <v>25.7465162574652</v>
+        <v>25.7957559681698</v>
       </c>
     </row>
   </sheetData>
@@ -666,13 +666,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7607DAB-6A72-43E6-B54E-1D8237459C16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19684780-F306-4E1A-BABA-48C7D91DC5FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758D6F04-1E2F-4E89-8990-FBCE07664245}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4E8592E-23BE-4F64-8FD2-BD1F79F3ED08}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59B74D7D-26AF-46DC-B215-FAAF998AD7D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FCDA6F4-1908-42CE-AEA3-4CD5331C1F33}"/>
 </file>
--- a/data/WP18/WP18_auswertung_parteien.xlsx
+++ b/data/WP18/WP18_auswertung_parteien.xlsx
@@ -389,13 +389,13 @@
         <v>3664</v>
       </c>
       <c r="C2" t="n">
-        <v>35.9153930131003</v>
+        <v>35.5526746724891</v>
       </c>
       <c r="D2" t="n">
-        <v>2800</v>
+        <v>2728</v>
       </c>
       <c r="E2" t="n">
-        <v>23.5807860262009</v>
+        <v>25.5458515283843</v>
       </c>
     </row>
     <row r="3">
@@ -406,13 +406,13 @@
         <v>2170</v>
       </c>
       <c r="C3" t="n">
-        <v>35.3691244239632</v>
+        <v>34.947004608295</v>
       </c>
       <c r="D3" t="n">
-        <v>1633</v>
+        <v>1572</v>
       </c>
       <c r="E3" t="n">
-        <v>24.7465437788019</v>
+        <v>27.5576036866359</v>
       </c>
     </row>
     <row r="4">
@@ -423,13 +423,13 @@
         <v>1508</v>
       </c>
       <c r="C4" t="n">
-        <v>36.779694757797</v>
+        <v>35.893899204244</v>
       </c>
       <c r="D4" t="n">
-        <v>1119</v>
+        <v>1051</v>
       </c>
       <c r="E4" t="n">
-        <v>25.7957559681698</v>
+        <v>30.3050397877984</v>
       </c>
     </row>
   </sheetData>
@@ -666,13 +666,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19684780-F306-4E1A-BABA-48C7D91DC5FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD2A165B-A3B9-4C0B-B343-CC22911BED20}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4E8592E-23BE-4F64-8FD2-BD1F79F3ED08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB4DD3F-291D-4203-B11E-BB74B329A2B5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FCDA6F4-1908-42CE-AEA3-4CD5331C1F33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A0A9BD5-3F61-43CC-905B-910DB43E8B8F}"/>
 </file>
--- a/data/WP18/WP18_auswertung_parteien.xlsx
+++ b/data/WP18/WP18_auswertung_parteien.xlsx
@@ -392,10 +392,10 @@
         <v>35.5526746724891</v>
       </c>
       <c r="D2" t="n">
-        <v>2728</v>
+        <v>2941</v>
       </c>
       <c r="E2" t="n">
-        <v>25.5458515283843</v>
+        <v>19.7325327510917</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         <v>34.947004608295</v>
       </c>
       <c r="D3" t="n">
-        <v>1572</v>
+        <v>1713</v>
       </c>
       <c r="E3" t="n">
-        <v>27.5576036866359</v>
+        <v>21.0599078341014</v>
       </c>
     </row>
     <row r="4">
@@ -426,10 +426,10 @@
         <v>35.893899204244</v>
       </c>
       <c r="D4" t="n">
-        <v>1051</v>
+        <v>1143</v>
       </c>
       <c r="E4" t="n">
-        <v>30.3050397877984</v>
+        <v>24.2042440318302</v>
       </c>
     </row>
   </sheetData>
@@ -666,13 +666,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD2A165B-A3B9-4C0B-B343-CC22911BED20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85ABDC10-373C-4661-93BA-2DAB4D74D631}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB4DD3F-291D-4203-B11E-BB74B329A2B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{327B6EB0-C373-4F01-BD02-10836EF02463}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A0A9BD5-3F61-43CC-905B-910DB43E8B8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE0C456A-E4A9-4264-8301-35C699E91249}"/>
 </file>